--- a/artfynd/A 1339-2026 artfynd.xlsx
+++ b/artfynd/A 1339-2026 artfynd.xlsx
@@ -1260,7 +1260,7 @@
         <v>133856914</v>
       </c>
       <c r="B7" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>133856915</v>
       </c>
       <c r="B8" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>133856913</v>
       </c>
       <c r="B9" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1339-2026 artfynd.xlsx
+++ b/artfynd/A 1339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>109716642</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,12 +784,7 @@
         <v>114677937</v>
       </c>
       <c r="B3" t="n">
-        <v>97539</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +828,10 @@
         <v>675149</v>
       </c>
       <c r="R3" t="n">
-        <v>7146434</v>
+        <v>7146438</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -906,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117286140</v>
+        <v>117286060</v>
       </c>
       <c r="B4" t="n">
-        <v>97725</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,14 +927,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtlänningstjärnen (Båtlänningstjärnen), Ly lm</t>
+          <t>Båtlänningstjärnen, Båtlänningstjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>675178</v>
+        <v>675140</v>
       </c>
       <c r="R4" t="n">
-        <v>7146377</v>
+        <v>7146400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,27 +991,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Örnberg</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Örnberg</t>
+          <t>Glenn Örnberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117286060</v>
+        <v>117286140</v>
       </c>
       <c r="B5" t="n">
-        <v>97819</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>675140</v>
+        <v>675178</v>
       </c>
       <c r="R5" t="n">
-        <v>7146400</v>
+        <v>7146377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,27 +1098,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Carina Örnberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Carina Örnberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117394267</v>
+        <v>133856913</v>
       </c>
       <c r="B6" t="n">
-        <v>97819</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,30 +1138,20 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rolands vägen, Ly lm</t>
+          <t>Vänjaurbäck, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>675149</v>
+        <v>675129</v>
       </c>
       <c r="R6" t="n">
-        <v>7146438</v>
+        <v>7146478</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,24 +1173,19 @@
           <t>Lycksele</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>AC-Lyc-0036</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>38 blommande 6 veg ,många utblommade</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,33 +1194,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Glenn Örnberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>133856914</v>
       </c>
       <c r="B7" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1317,7 @@
         <v>133856915</v>
       </c>
       <c r="B8" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1458,108 +1413,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>133856913</v>
-      </c>
-      <c r="B9" t="n">
-        <v>99077</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>233</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Vänjaurbäck, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>675129</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7146478</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1339-2026 artfynd.xlsx
+++ b/artfynd/A 1339-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109716642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114677937</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117286060</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117286140</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856913</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856914</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,8 +1448,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>